--- a/IMS/src/main/webapp/excelTemplate/blueIssueDetail.xlsx
+++ b/IMS/src/main/webapp/excelTemplate/blueIssueDetail.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\home\h1\excelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\innost\Desktop\IMS수정txt\excelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20700" windowHeight="12060" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="12060" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -76,10 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 작성일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 작성자</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -96,10 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>문제관리 상세</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>문제사항</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -289,6 +281,14 @@
   </si>
   <si>
     <t>${item.eFileRowName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제정보 상세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 등록일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -760,6 +760,99 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -772,101 +865,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1588,16 +1588,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="A1" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="I1" s="12"/>
       <c r="J1" s="12"/>
     </row>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="3" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B3" s="2"/>
     </row>
@@ -1633,128 +1633,128 @@
     </row>
     <row r="5" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+        <v>13</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
       <c r="F5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
+        <v>66</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
     </row>
     <row r="6" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+        <v>14</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
       <c r="F7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="A8" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
     </row>
     <row r="9" spans="1:10" ht="99.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="A9" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+        <v>29</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
       <c r="F11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
     </row>
     <row r="12" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+        <v>28</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
       <c r="F12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
+        <v>18</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
     </row>
     <row r="13" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14"/>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="14" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="8.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1785,81 +1785,81 @@
       <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="20" t="s">
+      <c r="A16" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="46"/>
+      <c r="C16" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="46"/>
+      <c r="E16" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="20" t="s">
+      <c r="F16" s="46"/>
+      <c r="G16" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="20" t="s">
+      <c r="H16" s="46"/>
+      <c r="I16" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="46"/>
     </row>
     <row r="17" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
+      <c r="A17" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21"/>
     </row>
     <row r="18" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="32"/>
+      <c r="C18" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="34"/>
+      <c r="E18" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="39" t="s">
+      <c r="F18" s="32"/>
+      <c r="G18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="41" t="s">
+      <c r="H18" s="34"/>
+      <c r="I18" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="42"/>
+      <c r="J18" s="34"/>
     </row>
     <row r="19" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="36"/>
+      <c r="A19" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="8.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1875,76 +1875,76 @@
       <c r="J22" s="6"/>
     </row>
     <row r="23" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="46"/>
+      <c r="D23" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="46"/>
     </row>
     <row r="24" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="29"/>
+      <c r="A24" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="21"/>
     </row>
     <row r="25" spans="1:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="D25" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="J25" s="42"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="34"/>
     </row>
     <row r="26" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="35"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="36"/>
+      <c r="A26" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="27"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="28"/>
     </row>
     <row r="27" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1965,92 +1965,98 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="22" t="s">
+      <c r="C30" s="44"/>
+      <c r="D30" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="24"/>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="44"/>
+      <c r="G30" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="45"/>
+      <c r="A31" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="37"/>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="34"/>
+      <c r="D32" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="44" t="s">
+      <c r="F32" s="34"/>
+      <c r="G32" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E32" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="J32" s="46" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="47"/>
+      <c r="A33" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="24"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="39"/>
     </row>
     <row r="34" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="I23:J23"/>
@@ -2058,12 +2064,6 @@
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="G11:J11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B5:E5"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="A16:B16"/>
